--- a/Ket_qua_hoa_don_final.xlsx
+++ b/Ket_qua_hoa_don_final.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Mẫu số_ 01 1748336096140.pdf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Mẫu số_ 01 1748350919543.pdf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Mẫu số_ 01 1748350919543.pdf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Mẫu số_ 01 1748350919543.pdf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>Mẫu số_ 01 1748350934340.pdf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>Mẫu số_ 01 1748350952077.pdf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>Mẫu số_ 01 1748350952077.pdf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>Mẫu số_ 01 1748404863977.pdf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
